--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -1,94 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Unreal\无尽战争公告更新\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView windowHeight="17920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t xml:space="preserve">  </t>
+    <t>编号</t>
   </si>
   <si>
-    <t xml:space="preserve">编号</t>
+    <t>详情英文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情英文</t>
+    <t>详情中文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情中文</t>
+    <t>详情日文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情日文</t>
+    <t>详情韩文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情韩文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version:V 0.1.6.3
+    <t>Version:V 0.1.6.3
 1.Enhance skill damage range;
 2.Make resources easier to obtain;
 3.Improve ad response speed;
 4.Fix several bugs.</t>
   </si>
   <si>
-    <t xml:space="preserve">版本号:V 0.1.6.3
+    <t>版本号:V 0.1.6.3
 1.增强技能伤害范围；
 2.资源获得更容易；
 3.提升广告响应速度：
-4.修复若干Bug。</t>
+4.修复若干Bug。5646654</t>
   </si>
   <si>
-    <t xml:space="preserve">バージョン:V 0.1.6.3
+    <t>バージョン:V 0.1.6.3
 1.スキルのダメージ範囲を強化；
 2.リソースの獲得を容易に；
 3.広告の応答速度を向上；
 4.いくつかのバグを修正。</t>
   </si>
   <si>
-    <t xml:space="preserve">버전:V 0.1.6.3
+    <t>버전:V 0.1.6.3
 1.스킬 피해 범위 강화；
 2.자원 획득 용이；
 3.광고 응답 속도 향상；
@@ -98,38 +80,375 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -152,32 +471,318 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -226,7 +831,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -259,26 +864,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -311,23 +899,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -469,65 +1040,60 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="0"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="40.394366197183096"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="42.647887323943664"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="50.42253521126761"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5.802816901408451"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58.08450704225352"/>
+    <col min="1" max="1" width="5.8" customWidth="1"/>
+    <col min="2" max="2" width="58.0846153846154" customWidth="1"/>
+    <col min="3" max="3" width="113.384615384615" customWidth="1"/>
+    <col min="4" max="4" width="42.6461538461538" customWidth="1"/>
+    <col min="5" max="5" width="50.4230769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="65" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -60,7 +60,7 @@
 1.增强技能伤害范围；
 2.资源获得更容易；
 3.提升广告响应速度：
-4.修复若干Bug。5646654</t>
+4.修复若干Bug。5646654fsddsfdssdfsdfs</t>
   </si>
   <si>
     <t>バージョン:V 0.1.6.3

--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -1,73 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Unreal\无尽战争公告更新\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView windowHeight="17920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t xml:space="preserve">  </t>
+    <t>编号</t>
   </si>
   <si>
-    <t xml:space="preserve">编号</t>
+    <t>详情英文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情英文</t>
+    <t>详情中文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情中文</t>
+    <t>详情日文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情日文</t>
+    <t>详情韩文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情韩文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version: V 0.1.6.4
+    <t>Version: V 0.1.6.4
 1. Enhanced skill damage range;  
 2. Easier resource acquisition;  
 3. Improved ad response speed;  
@@ -75,15 +57,15 @@
 5. Resolved several bugs.</t>
   </si>
   <si>
-    <t xml:space="preserve">版本号:V 0.1.6.4
+    <t>版本号:V 0.1.6.4
 1.增强技能伤害范围；
 2.资源获得更容易；
 3.提升广告响应速度;
 4.修复战斗中观看广告，导致游戏卡死的问题;
-5.修复若干Bug。</t>
+5.修复若干Bug。76554646</t>
   </si>
   <si>
-    <t xml:space="preserve">バージョン:V 0.1.6.4
+    <t>バージョン:V 0.1.6.4
 1.スキルのダメージ範囲を強化；
 2.リソースの獲得を容易に；
 3.広告の応答速度を向上；
@@ -91,7 +73,7 @@
 5.いくつかのバグを修正。</t>
   </si>
   <si>
-    <t xml:space="preserve">버전:V 0.1.6.4
+    <t>버전:V 0.1.6.4
 1.스킬 피해 범위 강화；
 2.자원 획득 용이；
 3.광고 응답 속도 향상；
@@ -102,38 +84,375 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -156,29 +475,318 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -227,7 +835,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -260,26 +868,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -312,23 +903,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -470,65 +1044,60 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="0"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5.802816901408451"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58.08450704225352"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="40.394366197183096"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="42.647887323943664"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="50.42253521126761"/>
+    <col min="1" max="1" width="5.8" customWidth="1"/>
+    <col min="2" max="2" width="58.0846153846154" customWidth="1"/>
+    <col min="3" max="3" width="40.3923076923077" customWidth="1"/>
+    <col min="4" max="4" width="42.6461538461538" customWidth="1"/>
+    <col min="5" max="5" width="50.4230769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="78" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -67,32 +67,36 @@
     <t xml:space="preserve">详情韩文</t>
   </si>
   <si>
-    <t xml:space="preserve">Version:V 0.1.6.3
-1.Enhance skill damage range;
-2.Make resources easier to obtain;
-3.Improve ad response speed;
-4.Fix several bugs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">版本号:V 0.1.6.3
+    <t xml:space="preserve">Version: V 0.1.6.4
+1. Enhanced skill damage range;  
+2. Easier resource acquisition;  
+3. Improved ad response speed;  
+4. Fixed the issue where watching ads during combat caused game crashes;  
+5. Resolved several bugs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">版本号:V 0.1.6.4
 1.增强技能伤害范围；
 2.资源获得更容易；
-3.提升广告响应速度：
-4.修复若干Bug。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バージョン:V 0.1.6.3
+3.提升广告响应速度;
+4.修复战斗中观看广告，导致游戏卡死的问题;
+5.修复若干Bug。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バージョン:V 0.1.6.4
 1.スキルのダメージ範囲を強化；
 2.リソースの獲得を容易に；
 3.広告の応答速度を向上；
-4.いくつかのバグを修正。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">버전:V 0.1.6.3
+4.戦闘中に広告を視聴するとゲームがフリーズする問題を修正；
+5.いくつかのバグを修正。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버전:V 0.1.6.4
 1.스킬 피해 범위 강화；
 2.자원 획득 용이；
 3.광고 응답 속도 향상；
-4.여러 버그 수정。</t>
+4.전투 중 광고 시청으로 게임이 멈추는 문제 수정；
+5.여러 버그 수정。</t>
   </si>
 </sst>
 </file>
@@ -156,15 +160,12 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,11 +487,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5.802816901408451"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58.08450704225352"/>
     <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="40.394366197183096"/>
     <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="42.647887323943664"/>
     <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="50.42253521126761"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5.802816901408451"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58.08450704225352"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,16 +515,16 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -1,89 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assets\打砖块文案\数据表格\更新公告\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView windowHeight="17920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t xml:space="preserve">  </t>
+    <t>编号</t>
   </si>
   <si>
-    <t xml:space="preserve">编号</t>
+    <t>详情英文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情英文</t>
+    <t>详情中文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情中文</t>
+    <t>详情日文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情日文</t>
+    <t>详情韩文</t>
   </si>
   <si>
-    <t xml:space="preserve">详情韩文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version: V 0.1.6.4
+    <t>Version: V 0.1.6.4
 1. Enhanced skill damage range;  
 2. Easier resource acquisition;  
 3. Improved ad response speed;  
 4. Fixed the issue where watching ads during combat caused game crashes;  
-5. Resolved several bugs.</t>
+5. Resolved several bugs.78987987</t>
   </si>
   <si>
-    <t xml:space="preserve">版本号:V 0.1.6.4
+    <t>版本号:V 0.1.6.4
 1.增强技能伤害范围；
 2.资源获得更容易；
 3.提升广告响应速度;
 4.修复战斗中观看广告，导致游戏卡死的问题;
-5.修复若干Bug。</t>
+5.修复若干Bug。7978978797897</t>
   </si>
   <si>
-    <t xml:space="preserve">バージョン:V 0.1.6.4
+    <t>バージョン:V 0.1.6.4
 1.スキルのダメージ範囲を強化；
 2.リソースの獲得を容易に；
 3.広告の応答速度を向上；
@@ -91,7 +73,7 @@
 5.いくつかのバグを修正。</t>
   </si>
   <si>
-    <t xml:space="preserve">버전:V 0.1.6.4
+    <t>버전:V 0.1.6.4
 1.스킬 피해 범위 강화；
 2.자원 획득 용이；
 3.광고 응답 속도 향상；
@@ -102,38 +84,375 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -156,29 +475,318 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -227,7 +835,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -260,26 +868,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -312,23 +903,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -470,65 +1044,60 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="0"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="5.802816901408451"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58.08450704225352"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="40.394366197183096"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="42.647887323943664"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="50.42253521126761"/>
+    <col min="1" max="1" width="5.8" customWidth="1"/>
+    <col min="2" max="2" width="58.0846153846154" customWidth="1"/>
+    <col min="3" max="3" width="40.3923076923077" customWidth="1"/>
+    <col min="4" max="4" width="42.6461538461538" customWidth="1"/>
+    <col min="5" max="5" width="50.4230769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="78" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>